--- a/04_DESIGN_TABLES/DesignTable_5600_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5600_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF7"/>
+  <dimension ref="A1:BF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | leg 1: male NPTF thread dia at L2 1.0589 vs hex flats 1.0600 (round end flush with the flats by 0.0005; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012); leg 2: male NPTF thread dia at L2 1.0589 vs hex flats 1.0600 (round end flush with the flats by 0.0005; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012); leg 3: male NPTF thread dia at L2 1.0589 vs hex flats 1.0600 (round end flush with the flats by 0.0005; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>leg 1: male NPTF thread dia at L2 1.0589 vs hex flats 1.0600 (round end flush with the flats by 0.0005; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012); leg 2: male NPTF thread dia at L2 1.0589 vs hex flats 1.0600 (round end flush with the flats by 0.0005; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012); leg 3: male NPTF thread dia at L2 1.0589 vs hex flats 1.0600 (round end flush with the flats by 0.0005; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -1862,12 +1862,408 @@
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | leg 1: male NPTF thread dia at L2 1.3259 vs hex flats 1.3100 (round end proud of the flats by 0.0079; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012); leg 2: male NPTF thread dia at L2 1.3259 vs hex flats 1.3100 (round end proud of the flats by 0.0079; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012); leg 3: male NPTF thread dia at L2 1.3259 vs hex flats 1.3100 (round end proud of the flats by 0.0079; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>leg 1: male NPTF thread dia at L2 1.3259 vs hex flats 1.3100 (round end proud of the flats by 0.0079; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012); leg 2: male NPTF thread dia at L2 1.3259 vs hex flats 1.3100 (round end proud of the flats by 0.0079; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012); leg 3: male NPTF thread dia at L2 1.3259 vs hex flats 1.3100 (round end proud of the flats by 0.0079; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
           <t>5600-16-16-16-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5600-20-20-20-FG</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.6267</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.74378</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.6267</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.74378</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.6267</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.74378</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>5600-20-20-20-FG</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Male Pipe Tee, 1 1/4-11 1/2 NPTF x 1 1/4-11 1/2 NPTF x 1 1/4-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>5600</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N1@DRIVE: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-20-20-20-FG column 'N1 LGTH' = 2.380 (catalog_verified.json); OMi Items row 1537: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; N2@DRIVE: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-20-20-20-FG column 'N2 LGTH' = 2.380 (catalog_verified.json); OMi Items row 1537: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; N3@DRIVE: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-20-20-20-FG column 'N3 LGTH' = 2.380 (catalog_verified.json); OMi Items row 1537: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; Y@HEX: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-20-20-20-FG column 'Y FLATS' = 1.625 (catalog_verified.json); OMi Items row 1537: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; D1@BORE: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-20-20-20-FG column 'A1 DRILL' = 1.250 (catalog_verified.json); OMi Items row 1537: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; D2@BORE: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-20-20-20-FG column 'A2 DRILL' = 1.250 (catalog_verified.json); OMi Items row 1537: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; D3@BORE: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-20-20-20-FG column 'A3 DRILL' = 1.250 (catalog_verified.json); OMi Items row 1537: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; THDMAJ_A1@DRIVE: ASME B1.20.1 / B1.20.3 1-1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[20] pipe OD for the part-number dash -20 (OMi Items!U1537 "1 1/4-11 1/2 NPTF", catalog 1-1/4-11-1/2); equals the 2026-10-02 proposal; THDMAJ_A2@DRIVE: ASME B1.20.1 / B1.20.3 1-1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[20] pipe OD for the part-number dash -20 (OMi Items!U1537 "1 1/4-11 1/2 NPTF", catalog 1-1/4-11-1/2); equals the 2026-10-02 proposal; THDMAJ_A3@DRIVE: ASME B1.20.1 / B1.20.3 1-1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[20] pipe OD for the part-number dash -20 (OMi Items!U1537 "1 1/4-11 1/2 NPTF", catalog 1-1/4-11-1/2); equals the 2026-10-02 proposal; $PRP@Threads: ASME B1.20.1 / B1.20.3 1-1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[20] thread text, format of the built 5600 rows; equals the 2026-10-02 proposal | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): every body size from the Brennan TFA catalog alone | leg 1: male NPTF thread dia at L2 1.6709 vs hex flats 1.6250 (round end proud of the flats by 0.0229; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012); leg 2: male NPTF thread dia at L2 1.6709 vs hex flats 1.6250 (round end proud of the flats by 0.0229; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012); leg 3: male NPTF thread dia at L2 1.6709 vs hex flats 1.6250 (round end proud of the flats by 0.0229; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>5600-20-20-20-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5600-24-24-24-FG</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.86566</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.86326</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.86566</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.86326</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.86566</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.86326</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>5600-24-24-24-FG</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Male Pipe Tee, 1 1/2-11 1/2 NPTF x 1 1/2-11 1/2 NPTF x 1 1/2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>5600</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N1@DRIVE: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-24-24-24-FG column 'N1 LGTH' = 2.640 (catalog_verified.json); OMi Items row 1538: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; N2@DRIVE: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-24-24-24-FG column 'N2 LGTH' = 2.640 (catalog_verified.json); OMi Items row 1538: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; N3@DRIVE: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-24-24-24-FG column 'N3 LGTH' = 2.640 (catalog_verified.json); OMi Items row 1538: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; Y@HEX: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-24-24-24-FG column 'Y FLATS' = 1.875 (catalog_verified.json); OMi Items row 1538: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; D1@BORE: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-24-24-24-FG column 'A1 DRILL' = 1.500 (catalog_verified.json); OMi Items row 1538: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; D2@BORE: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-24-24-24-FG column 'A2 DRILL' = 1.500 (catalog_verified.json); OMi Items row 1538: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; D3@BORE: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-24-24-24-FG column 'A3 DRILL' = 1.500 (catalog_verified.json); OMi Items row 1538: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; THDMAJ_A1@DRIVE: ASME B1.20.1 / B1.20.3 1-1/2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[24] pipe OD for the part-number dash -24 (OMi Items!U1538 "1 1/2-11 1/2 NPFT", catalog 1-1/2-11-1/2); equals the 2026-10-02 proposal; THDMAJ_A2@DRIVE: ASME B1.20.1 / B1.20.3 1-1/2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[24] pipe OD for the part-number dash -24 (OMi Items!U1538 "1 1/2-11 1/2 NPFT", catalog 1-1/2-11-1/2); equals the 2026-10-02 proposal; THDMAJ_A3@DRIVE: ASME B1.20.1 / B1.20.3 1-1/2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[24] pipe OD for the part-number dash -24 (OMi Items!U1538 "1 1/2-11 1/2 NPFT", catalog 1-1/2-11-1/2); equals the 2026-10-02 proposal; $PRP@Threads: ASME B1.20.1 / B1.20.3 1-1/2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[24] thread text, format of the built 5600 rows; equals the 2026-10-02 proposal | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): every body size from the Brennan TFA catalog alone | leg 1: male NPTF thread dia at L2 1.9109 vs hex flats 1.8750 (round end proud of the flats by 0.0179; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012); leg 2: male NPTF thread dia at L2 1.9109 vs hex flats 1.8750 (round end proud of the flats by 0.0179; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012); leg 3: male NPTF thread dia at L2 1.9109 vs hex flats 1.8750 (round end proud of the flats by 0.0179; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>5600-24-24-24-FG</t>
         </is>
       </c>
     </row>
